--- a/WorkBot/refactor-experimental/data/orders/A.L. George/A.L. George_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/A.L. George/A.L. George_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Essentia Water</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Evian 1L</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>23.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>46.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Fiji Water 1L</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>16.50</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>33.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Fiji Water 500ml</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>37.00</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/A.L. George/A.L. George_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/A.L. George/A.L. George_Triphammer_20251114.xlsx
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>16.5</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="3">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
